--- a/artfynd/A 40568-2025 artfynd.xlsx
+++ b/artfynd/A 40568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,9 +790,465 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137518229</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>630280</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6643187</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518229</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137518228</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98300</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>630274</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6643182</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åland</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518228</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137518230</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98300</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>630315</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6643192</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518230</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137518231</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101651</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>630318</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6643217</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Annika Leers</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137518231</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2025 artfynd.xlsx
+++ b/artfynd/A 40568-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137518229</v>
       </c>
       <c r="B3" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137518228</v>
       </c>
       <c r="B4" t="n">
-        <v>98300</v>
+        <v>98303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137518230</v>
       </c>
       <c r="B5" t="n">
-        <v>98300</v>
+        <v>98303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137518231</v>
       </c>
       <c r="B6" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
